--- a/VerveStacks_NGA_grids_kan10/SuppXLS/Scen_TSParameters_ts_60c.xlsx
+++ b/VerveStacks_NGA_grids_kan10/SuppXLS/Scen_TSParameters_ts_60c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FE4E1F8-BC1F-4A02-AF83-78A08A7A507D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{112B19B1-1FF7-4B0B-A4D1-EEC3BA1358E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -885,13 +885,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH06,S02aH03,S05aH07,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S04aH06,S05aH04,S06aH02,S06aH03,S01aH04,S01aH07,S02aH07,S03aH02,S04aH02,S04aH05,S04aH08,S02aH04,S02aH05,S06aH07,S01aH02,S04aH04,S01aH03,S05aH02,S05aH03,S05aH06,S02aH02,S06aH06,S03aH04,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S04aH03,S05aH08,S03aH03</t>
+    <t>S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S01aH04,S01aH07,S02aH07,S01aH06,S02aH03,S05aH07,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH04,S02aH05,S06aH07,S02aH02,S06aH06,S01aH02,S04aH04,S03aH04,S04aH05,S04aH08,S03aH02,S04aH03,S03aH03,S05aH08,S04aH06,S05aH04,S06aH02,S06aH03,S01aH03,S05aH02,S05aH03,S05aH06</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH01,S04aH01,S06aH02,S01aH02,S05aH10,S06aH09,S01aH09,S04aH02,S01aH10,S03aH02,S05aH08,S03aH08,S03aH10,S06aH08,S01aH08,S02aH08,S03aH01,S02aH09,S04aH09,S05aH01,S03aH09,S05aH09,S02aH01,S02aH10,S05aH02,S04aH08,S06aH01,S02aH02,S04aH10,S06aH10</t>
+    <t>S01aH10,S03aH02,S01aH02,S05aH10,S01aH09,S01aH01,S04aH01,S06aH02,S03aH09,S05aH09,S03aH08,S03aH10,S06aH08,S03aH01,S01aH08,S02aH08,S02aH09,S04aH09,S05aH01,S05aH08,S04aH02,S02aH01,S02aH10,S05aH02,S02aH02,S04aH10,S06aH10,S04aH08,S06aH01,S06aH09</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S01aH01,S04aH01,S06aH02,S01aH02,S05aH10,S06aH09,S01aH09,S04aH02,S01aH10,S03aH02,S05aH08,S03aH08,S03aH10,S06aH08,S01aH08,S02aH08,S03aH01,S02aH09,S04aH09,S05aH01,S03aH09,S05aH09,S02aH01,S02aH10,S05aH02,S04aH08,S06aH01,S02aH02,S04aH10,S06aH10</v>
+        <v>S01aH10,S03aH02,S01aH02,S05aH10,S01aH09,S01aH01,S04aH01,S06aH02,S03aH09,S05aH09,S03aH08,S03aH10,S06aH08,S03aH01,S01aH08,S02aH08,S02aH09,S04aH09,S05aH01,S05aH08,S04aH02,S02aH01,S02aH10,S05aH02,S02aH02,S04aH10,S06aH10,S04aH08,S06aH01,S06aH09</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S01aH06,S02aH03,S05aH07,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S04aH06,S05aH04,S06aH02,S06aH03,S01aH04,S01aH07,S02aH07,S03aH02,S04aH02,S04aH05,S04aH08,S02aH04,S02aH05,S06aH07,S01aH02,S04aH04,S01aH03,S05aH02,S05aH03,S05aH06,S02aH02,S06aH06,S03aH04,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S04aH03,S05aH08,S03aH03</v>
+        <v>S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S01aH04,S01aH07,S02aH07,S01aH06,S02aH03,S05aH07,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH04,S02aH05,S06aH07,S02aH02,S06aH06,S01aH02,S04aH04,S03aH04,S04aH05,S04aH08,S03aH02,S04aH03,S03aH03,S05aH08,S04aH06,S05aH04,S06aH02,S06aH03,S01aH03,S05aH02,S05aH03,S05aH06</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1614,7 +1614,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61262DC9-1B54-4792-BD39-E9CAA51A65A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB906D8F-4755-4579-B21D-252B77E9E7C3}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1758,7 +1758,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7C2E779-51ED-4FC9-88B0-0E10A4C407EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA67FA83-D750-4006-851D-8D5DE3CF859C}">
   <dimension ref="B9:O2170"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -58700,7 +58700,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7028709-E2CF-49AC-A71D-BA75BC0638C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B0B067A-637A-429A-9D40-CE5F6BD37D69}">
   <dimension ref="B9:IV83"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -88562,7 +88562,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8F3D0B8-451D-41DF-9417-35D256380FA9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2543782A-A5A1-483F-90E9-2B246A23DFAB}">
   <dimension ref="B9:E70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -89432,7 +89432,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{508C4B5F-BACF-4685-9279-7CC4917A8D03}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26597A44-5FA8-4E47-AFD5-618C66D5EF88}">
   <dimension ref="B9:D130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -90779,7 +90779,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC368311-B694-4D73-AF6E-76F8DB0C6A21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B33CBF1-CEF6-423C-A2DC-3ADEDCAF3E44}">
   <dimension ref="B9:D70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -91466,7 +91466,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D578026-DCB3-41CC-AC33-BA8AE17AE2C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{143C9ADE-15DB-45E5-96C9-4AF09FB6F87C}">
   <dimension ref="B9:E184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
